--- a/____EvoM1_TraitTable/cellcounts_selected.xlsx
+++ b/____EvoM1_TraitTable/cellcounts_selected.xlsx
@@ -4641,12 +4641,6 @@
       <c r="H79">
         <v>16977183580</v>
       </c>
-      <c r="I79">
-        <v>0.0641012667383097</v>
-      </c>
-      <c r="J79">
-        <v>55.3941435722781</v>
-      </c>
       <c r="N79" t="inlineStr">
         <is>
           <t>HerculanoHouzel_etal_2015_Table1</t>
@@ -4675,16 +4669,6 @@
       <c r="S79" t="inlineStr">
         <is>
           <t>HerculanoHouzel_etal_2015_Table5</t>
-        </is>
-      </c>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>DosSantos_etal_2020_Table1</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>DosSantos_etal_2020_Table1</t>
         </is>
       </c>
     </row>
@@ -4943,8 +4927,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="66af2654134d243f62aac8e2b322f1d6">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2bc3adf68671d86faa9c37249f400344" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d42a73f51a03135be35f4acb272f8cf1">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2ea21b36c10eaa86a5cb337ec7f4e0a6" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
     <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
     <xsd:element name="properties">
@@ -4968,6 +4952,8 @@
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -5042,6 +5028,16 @@
     <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -5195,9 +5191,9 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7779C4C4-B6BD-47D7-AA37-ADC5946B5F8D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E9A0AF1-E8B0-44BB-A626-0F83D6EFA2B8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC6DCB53-2A2C-4F39-AD50-F7E1A6CFE903}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{241E26B0-CBD3-440F-BCC9-917114D1520E}"/>
 </file>
--- a/____EvoM1_TraitTable/cellcounts_selected.xlsx
+++ b/____EvoM1_TraitTable/cellcounts_selected.xlsx
@@ -21409,13 +21409,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9429C2B-2C61-47A2-82AA-11A5EC938566}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C821BCB-6CB5-4E1D-A024-28A7177AD42C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{776455F4-945C-40CA-B4CB-4C8724E4EABF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74B12FC4-C0BB-4E03-AB58-8C486EC468ED}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2FD6719-6136-40D4-9777-5B486889DC05}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73EF7E0B-A816-480A-8363-E768DADE14E4}"/>
 </file>
--- a/____EvoM1_TraitTable/cellcounts_selected.xlsx
+++ b/____EvoM1_TraitTable/cellcounts_selected.xlsx
@@ -21409,13 +21409,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C821BCB-6CB5-4E1D-A024-28A7177AD42C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3CD6DEF-2D0D-4F2C-8DD3-69169B3B4766}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74B12FC4-C0BB-4E03-AB58-8C486EC468ED}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDE88749-99A3-4BB6-94F7-9C41AAB257B0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73EF7E0B-A816-480A-8363-E768DADE14E4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADC25B90-828C-43B7-A0E4-D31C0C13E9B5}"/>
 </file>
--- a/____EvoM1_TraitTable/cellcounts_selected.xlsx
+++ b/____EvoM1_TraitTable/cellcounts_selected.xlsx
@@ -21409,13 +21409,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3CD6DEF-2D0D-4F2C-8DD3-69169B3B4766}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9470467E-7F05-4809-895F-BFAE20D7B4B5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDE88749-99A3-4BB6-94F7-9C41AAB257B0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{179C7175-620B-43BD-8F68-94916E94E351}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADC25B90-828C-43B7-A0E4-D31C0C13E9B5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{624D10ED-A23A-459A-9BA9-7DEA842F1091}"/>
 </file>
--- a/____EvoM1_TraitTable/cellcounts_selected.xlsx
+++ b/____EvoM1_TraitTable/cellcounts_selected.xlsx
@@ -21409,13 +21409,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9470467E-7F05-4809-895F-BFAE20D7B4B5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9B507E4-5104-46C5-A5D9-58DC79806D9D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{179C7175-620B-43BD-8F68-94916E94E351}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{977D2830-722F-4033-8FD8-A5A2041A28CF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{624D10ED-A23A-459A-9BA9-7DEA842F1091}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50466091-E930-4EE9-8C83-644BA255A9F1}"/>
 </file>
--- a/____EvoM1_TraitTable/cellcounts_selected.xlsx
+++ b/____EvoM1_TraitTable/cellcounts_selected.xlsx
@@ -21409,13 +21409,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9B507E4-5104-46C5-A5D9-58DC79806D9D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8049A602-58CF-41E3-B02E-032D19C5EFB6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{977D2830-722F-4033-8FD8-A5A2041A28CF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17ADC2A3-C291-4C3F-8885-5E2214BE1FB8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50466091-E930-4EE9-8C83-644BA255A9F1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1D7C9E6-C320-40C7-8527-E2899567009F}"/>
 </file>
--- a/____EvoM1_TraitTable/cellcounts_selected.xlsx
+++ b/____EvoM1_TraitTable/cellcounts_selected.xlsx
@@ -21409,13 +21409,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8049A602-58CF-41E3-B02E-032D19C5EFB6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA78F752-08E7-468B-A57B-E42CA08FFEFC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17ADC2A3-C291-4C3F-8885-5E2214BE1FB8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F0CED895-CF4D-4632-8C0C-C08CD90B79D7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1D7C9E6-C320-40C7-8527-E2899567009F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10F4F25A-0655-426B-AEFB-7670C02755A1}"/>
 </file>
--- a/____EvoM1_TraitTable/cellcounts_selected.xlsx
+++ b/____EvoM1_TraitTable/cellcounts_selected.xlsx
@@ -21409,13 +21409,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA78F752-08E7-468B-A57B-E42CA08FFEFC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8E43DDF-E2C0-4898-ADB1-5E2FBAC40B40}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F0CED895-CF4D-4632-8C0C-C08CD90B79D7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA746FF0-FED4-49DC-8A24-9DD39FE60BE3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10F4F25A-0655-426B-AEFB-7670C02755A1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12BA10C6-3630-4ACA-BD94-2F3F3F8AD7AC}"/>
 </file>
--- a/____EvoM1_TraitTable/cellcounts_selected.xlsx
+++ b/____EvoM1_TraitTable/cellcounts_selected.xlsx
@@ -21409,13 +21409,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8E43DDF-E2C0-4898-ADB1-5E2FBAC40B40}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCB564C2-F61A-440C-9885-72BCD1539E35}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA746FF0-FED4-49DC-8A24-9DD39FE60BE3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF563ED-AC67-4117-AE54-0712A4C4D1C5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12BA10C6-3630-4ACA-BD94-2F3F3F8AD7AC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E622217-FC93-4DA9-9BE1-04F7036A1A14}"/>
 </file>
--- a/____EvoM1_TraitTable/cellcounts_selected.xlsx
+++ b/____EvoM1_TraitTable/cellcounts_selected.xlsx
@@ -21409,13 +21409,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCB564C2-F61A-440C-9885-72BCD1539E35}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2EF1C37-92A8-4FBC-965A-670D87771694}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF563ED-AC67-4117-AE54-0712A4C4D1C5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B223246-6430-4C60-9B31-859EAAF8E7F1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E622217-FC93-4DA9-9BE1-04F7036A1A14}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E0D3E6A-3A4E-4CA8-87E2-1C5C7AD1E812}"/>
 </file>
--- a/____EvoM1_TraitTable/cellcounts_selected.xlsx
+++ b/____EvoM1_TraitTable/cellcounts_selected.xlsx
@@ -21409,13 +21409,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2EF1C37-92A8-4FBC-965A-670D87771694}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19C7B8AA-CBDE-4C61-92D9-B8576A684486}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B223246-6430-4C60-9B31-859EAAF8E7F1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A689679-931B-4B65-A2E8-043262B5193B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E0D3E6A-3A4E-4CA8-87E2-1C5C7AD1E812}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF1DEE4E-09AA-4B24-BD2D-42E5C1A00BC5}"/>
 </file>
--- a/____EvoM1_TraitTable/cellcounts_selected.xlsx
+++ b/____EvoM1_TraitTable/cellcounts_selected.xlsx
@@ -21409,13 +21409,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19C7B8AA-CBDE-4C61-92D9-B8576A684486}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D03F5C97-E7B3-4F26-845B-7127D8F2B456}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A689679-931B-4B65-A2E8-043262B5193B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DFF34E2-F89D-4FCB-9A63-5C33466F8733}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF1DEE4E-09AA-4B24-BD2D-42E5C1A00BC5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EEA2F7CD-D17F-43C3-ACD8-8271A652F0E9}"/>
 </file>
--- a/____EvoM1_TraitTable/cellcounts_selected.xlsx
+++ b/____EvoM1_TraitTable/cellcounts_selected.xlsx
@@ -21409,13 +21409,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D03F5C97-E7B3-4F26-845B-7127D8F2B456}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B09F02F4-B495-43FB-BC63-5F43CFECF5C9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DFF34E2-F89D-4FCB-9A63-5C33466F8733}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94D48386-1042-4508-94A3-3E1F60C77F45}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EEA2F7CD-D17F-43C3-ACD8-8271A652F0E9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{487D05A7-1E23-4D0C-BFE3-01660A78D12A}"/>
 </file>
--- a/____EvoM1_TraitTable/cellcounts_selected.xlsx
+++ b/____EvoM1_TraitTable/cellcounts_selected.xlsx
@@ -21409,13 +21409,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B09F02F4-B495-43FB-BC63-5F43CFECF5C9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B60F0624-E6EB-43A4-B27B-F7F3E2307EED}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94D48386-1042-4508-94A3-3E1F60C77F45}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED7071E9-E35D-40A6-9F70-79E5CCA5E49C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{487D05A7-1E23-4D0C-BFE3-01660A78D12A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D328EAAC-496D-43CB-8487-8ABBD9F65887}"/>
 </file>
--- a/____EvoM1_TraitTable/cellcounts_selected.xlsx
+++ b/____EvoM1_TraitTable/cellcounts_selected.xlsx
@@ -21409,13 +21409,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B60F0624-E6EB-43A4-B27B-F7F3E2307EED}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CECA1B4-E459-4C24-95BE-A81C4DD38860}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED7071E9-E35D-40A6-9F70-79E5CCA5E49C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C38D4804-851B-4F26-B650-FBA3406E8C79}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D328EAAC-496D-43CB-8487-8ABBD9F65887}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2CD1D0F-F0AC-4D31-9951-534EC65EDC62}"/>
 </file>
--- a/____EvoM1_TraitTable/cellcounts_selected.xlsx
+++ b/____EvoM1_TraitTable/cellcounts_selected.xlsx
@@ -28739,4 +28739,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2D195B3-FA49-4BD5-A728-657CEADB3AA9}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29384E65-CE6E-4AB0-BB25-D0E20BAF88AE}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2576F16-5BAA-429A-A82C-A1C4EF2AA393}"/>
 </file>
--- a/____EvoM1_TraitTable/cellcounts_selected.xlsx
+++ b/____EvoM1_TraitTable/cellcounts_selected.xlsx
@@ -29017,13 +29017,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2D195B3-FA49-4BD5-A728-657CEADB3AA9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D7D2939-18F6-415F-B101-B008C4D4F818}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29384E65-CE6E-4AB0-BB25-D0E20BAF88AE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47FFE5AC-5307-442A-AC97-8E538687DE8B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2576F16-5BAA-429A-A82C-A1C4EF2AA393}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20F58BF0-3BBC-4BDD-B284-C710D77BB2E1}"/>
 </file>